--- a/errori.xlsx
+++ b/errori.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0839d1ad85cbfb9d/Documenti/test web pag/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{AF60C3D4-B50F-491F-8355-E8E71D8728BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B473BAD-C57C-4E78-8B69-CFF629C6FD18}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{AF60C3D4-B50F-491F-8355-E8E71D8728BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9292C51-39BA-4490-96E1-7A2E0E21B157}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{BD21F36C-7E0F-426B-9586-72325EAA4206}"/>
   </bookViews>
   <sheets>
-    <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
+    <sheet name="errori" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -124,6 +124,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/errori.xlsx
+++ b/errori.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0839d1ad85cbfb9d/Documenti/test web pag/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luca\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{AF60C3D4-B50F-491F-8355-E8E71D8728BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9292C51-39BA-4490-96E1-7A2E0E21B157}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F9F5A4-083A-40FF-93AE-D70C5053F641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{BD21F36C-7E0F-426B-9586-72325EAA4206}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A57C2007-4DF2-4BB1-93DB-62C40DE8617B}"/>
   </bookViews>
   <sheets>
     <sheet name="errori" sheetId="1" r:id="rId1"/>
@@ -36,49 +36,868 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>errore</t>
-  </si>
-  <si>
-    <t>descriz</t>
-  </si>
-  <si>
-    <t>aiuto1</t>
-  </si>
-  <si>
-    <t>aiuto2</t>
-  </si>
-  <si>
-    <t>err1</t>
-  </si>
-  <si>
-    <t>err2</t>
-  </si>
-  <si>
-    <t>xa</t>
-  </si>
-  <si>
-    <t>xb</t>
-  </si>
-  <si>
-    <t>xc</t>
-  </si>
-  <si>
-    <t>ya</t>
-  </si>
-  <si>
-    <t>yb</t>
-  </si>
-  <si>
-    <t>yc</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="285">
+  <si>
+    <t>\</t>
+  </si>
+  <si>
+    <t>"01"Scaduto tempo conteggio IS/ID in grande veloc.conteggio IS/ID in grande veloc.</t>
+  </si>
+  <si>
+    <t>SU IMPIANTI IDRAULICI VERIFICARE FUNZIONAMENTO VALVOLA ALTA VELOCITA' , SE NON ARRIVA ALIMENTAZIONE VERIFICARE IL CIRCUITO CHE LA COMANDA . NELLE VARIE TIPOLOGIE DI IMPIANTI PUO' ESSERE COMANDATA DAL  RELE' "KV" COLLEGATO SU MORSETTO SCHEDA 1B \ K, VERIFICARE CHE ARRIVI TENSIONE ALLA BOBINA DEL RELE' KV, SE NON ARRIVA TENSIONE VERIFICARE SULLA DOCUMENTAZIONE DEL QUADRO L' USCITA DELLA SCHEDA CHE LO COMANDA, SE CI SONO ALTRE USCITE DELLO STESSO TIPO LIBERE TRAMITE PROG2 SPOSTARE FUNZIONE ALTA VELOCITA' SU UNA DI QUESTE E SPOSTARE IL FILO SUL MORSETTO DEDICATO. SU IMPIANTI 81\20 LA VALVOLA VIENE COMANDATA DAL CONTATTO DEL RELE' "PP" A BORDO SCHEDA, VERIFICARE TENSIONE IN USCITA SU P2</t>
+  </si>
+  <si>
+    <t>SU IMPIANTI GRL VERIFICARE SEGNALI VELOCITA' SU INVERTER , VERIFICARE SE TUTTE LE USCITE DELLA 1R FUNZIONANO CORRETTAMENTE . IN GENERE R4 RIMANE LIBERA E SI PUO' USARE MODIFICANDO LA PROGRAMMAZIONE CODICE VELOCITA' PER SOSTITUIRE UN EVENTUALE USCITA DIFETTOSA</t>
+  </si>
+  <si>
+    <t>SU IMPIANTI 3VF ERIFICARE SE L' IMPIANTO NON SI FERMA IN STALLO DOPO IL CAMBIO VELOCITA' , IN QUESTO CASO VERIFICARE SE RICEVE IL SEGNALE DI BASSA , NEL CASO I SEGNALI SIANO OK  VERIFICARE PROGRAMMAZIONI INVERTER E IN CASO DI MOTORE GEARED AD ANELLO APERTO ACCERTARSI DI AVER FATTO APPRENDIMENTO MOTORE E NEL CASO RIFARLO .</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>"02" Protezione termica motore ingresso TS</t>
+  </si>
+  <si>
+    <t>VERIFICARE LED "TS" ( SULLA 1B IN BASSO A DESTRA O SULLA K SUL LATO DESTRO DELLA SCHEDA ) . IN CASO DI LED SPENTO VERIFICARE SE IL MOTORE RISULTA CALDO E L' INTERVENTO DEL TERMISTORE E' GIUSTIFICATO. SE IL MOTORE RISULTA AD UNA TEMPERATURA ACCETTABILE  SOLO PER PROVA FARE UN PONTE TRA "-S" E "TS", IL LED SI DEVE ACCENDERE E PREMENDO IL TASTO MODE DELLA SCHEDA SI DEVE RESETTARE L' ERRORE. A QUESTO PUNTO BISOGNA VERIFICARE IL CABLAGGIO DEL TERMISTORE  E RIPRISTINARE IL COLLEGAMENTO ORIGINALE ELIMINANDO IL PONTE MESSO DURANTE LA PROVA</t>
+  </si>
+  <si>
+    <t>ATTENZIONE IN CASO CON IL PONTE "-S" E "TS" IL LED TS RIMANGA SPENTO VERIFICARE LE RESTISTENZE SULLA SCHEDA VICINO AL MORSETTO TS, SE RISULTANO DANNEGGIATE PRIMA DI FARE QUALSIASI COSA VERIFICARE IL CABLAGGIO DEL TERMISTORE MOTORE SPECIALMENTE CON MOTORI GRL CAPITATO PIU' VOLTE UN CABLAGGIO ERRATO LATO MOTORE , QUESTO SPESSO DANNEGGIA LA SCHEDA IN MODO IRRIPARABILE QUINDI SE NON SI INTERVIENE A CORREGGERE IL PROBLEMA SI VA IN CONTRO ALLA ROTTURA DELL EVENTUALE NUOVA SCHEDA . ESEGUITI TUTTI I CONTROLLI CONTATTARE ASSISTENZA PER EVENTUALE SOSTITUZIONE DELLA SCHEDA .</t>
+  </si>
+  <si>
+    <t>ERR 02SECONDO CASO</t>
+  </si>
+  <si>
+    <t>"03" Protezione termica olio ingresso TC</t>
+  </si>
+  <si>
+    <t>PIPPO1</t>
+  </si>
+  <si>
+    <t>ERR 03 SECONDO CASO</t>
+  </si>
+  <si>
+    <t>"04" Pressostato mandata olio ingresso PS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ok199 </t>
+  </si>
+  <si>
+    <t>ERR 01 PRIMO CASO</t>
+  </si>
+  <si>
+    <t>ERR 01 SECONDO CASO</t>
+  </si>
+  <si>
+    <t>ERR 01 TERZO CASO</t>
+  </si>
+  <si>
+    <t>"05" ERR05</t>
+  </si>
+  <si>
+    <t>ok1YYY OK 11 55</t>
+  </si>
+  <si>
+    <t>"06" Mancanza fase o errata sequenza ingr. L1/L2/L3</t>
+  </si>
+  <si>
+    <t>ok6 OK</t>
+  </si>
+  <si>
+    <t>"07" Sovraccarico in cabina ingresso CE</t>
+  </si>
+  <si>
+    <t>ok7</t>
+  </si>
+  <si>
+    <t>"08" Blocco per accesso in fossa FI74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SU IMPIANTI 81\20 ERRORE DOVUTO A INTERVENTO CONTATTO SU PORTA PIANO INFERIORE ( MORSETTO CP0 DEL QUADRO ) . Con intervento conttatto la scheda segnala errore "F08" , mettendo manutenzione fossa la scheda segnala "9.08" . Se si resetta errore mentre è in manutenzione fossa la scheda cancella errore ma nel momento in cui si toglie la manutenzione fossa la scheda torna a segnalare "F08" . Per resettare l' errore oltre al pulsante mode sulla scheda è possibile  azionare il contatto del piano inferiore tramite chiave di sblocco , mantenerla fino a quando la gemma occupato rimane fissa , a quel punto rilasciare la chiave .  ( fatta nuova cpu b360 vignati per impedire reset con porte aperte ) ,  </t>
+  </si>
+  <si>
+    <t>ATTENZIONE : la scheda segnala  "F08" anche se il morsetto test freni è in posizione CF1\CF2 e si aziona la manutenzione di fossa . SPOSTARE CONNETTORE SU "-\CTF" o togliere la manutenzione</t>
+  </si>
+  <si>
+    <t>"09" Pulsante chiusura  porte sempre chiuso</t>
+  </si>
+  <si>
+    <t>ok9</t>
+  </si>
+  <si>
+    <t>"10" Non esce dal piano dopo comando partenza</t>
+  </si>
+  <si>
+    <t>ok10</t>
+  </si>
+  <si>
+    <t>"11" Seriale non arrivano dati al PROG.</t>
+  </si>
+  <si>
+    <t>ok11</t>
+  </si>
+  <si>
+    <t>"12" Seriale cabina</t>
+  </si>
+  <si>
+    <t>ok12DRRTT</t>
+  </si>
+  <si>
+    <t>"13" Seriale espansione quadro</t>
+  </si>
+  <si>
+    <t>ok13hujuj</t>
+  </si>
+  <si>
+    <t>"14"  ERR14</t>
+  </si>
+  <si>
+    <t>ok14</t>
+  </si>
+  <si>
+    <t>"15" ERR15</t>
+  </si>
+  <si>
+    <t>ok15</t>
+  </si>
+  <si>
+    <t>"16" Ingresso bypass chiuso senza emergenza</t>
+  </si>
+  <si>
+    <t>ok16</t>
+  </si>
+  <si>
+    <t>"17" Pulsante piano  incastrato</t>
+  </si>
+  <si>
+    <t>ok17</t>
+  </si>
+  <si>
+    <t>"18" Pulsante cabina incastrato</t>
+  </si>
+  <si>
+    <t>ok18</t>
+  </si>
+  <si>
+    <t>"19" Rifasatore SR azionato ad un piano intermedio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ok19  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IN CASO DI MAGNETI SU STAFFA STEM E PROBLEMI INTERVENTO RIFASATORI VERIFICARE CHE I MAGNETI SIANO POSTI ALL ESTREMITA DELLA STAFFETTA </t>
+  </si>
+  <si>
+    <t>"20" Rifasatore DR azionato ad un piano intermedio</t>
+  </si>
+  <si>
+    <t>"21" Rifasatori SR e DR entrambi azionati</t>
+  </si>
+  <si>
+    <t>ok21</t>
+  </si>
+  <si>
+    <t>"22" Rif SR non azionato con posiz.  =  estremo sup.</t>
+  </si>
+  <si>
+    <t>ok22</t>
+  </si>
+  <si>
+    <t>"23" Rif DR non azionato con posiz.  = estremo inf.</t>
+  </si>
+  <si>
+    <t>ok23</t>
+  </si>
+  <si>
+    <t>"24" Controllo sic.  aperto al piano ingresso CS</t>
+  </si>
+  <si>
+    <t>ok24</t>
+  </si>
+  <si>
+    <t>"25" Controllo sic.  ch. fuori piano ingresso CS</t>
+  </si>
+  <si>
+    <t>ok25</t>
+  </si>
+  <si>
+    <t>"26" Teleruttori non caduti prima delcomando  ingr.CT</t>
+  </si>
+  <si>
+    <t>ok26</t>
+  </si>
+  <si>
+    <t>"27" Teleruttori non eccitati o ingr.CT sempre chiuso</t>
+  </si>
+  <si>
+    <t>ok27</t>
+  </si>
+  <si>
+    <t>VERIFICARE PROGRAMMAZIONE INGRESSO CT  ( 5.0.05 = 67 ). SU GRL  SENZA INGRESSO PROGRAMMATO SI FERMA SU PRIMO MAGNETE DI FERMATA , DA ERRORE 27  , RESETTANDO ERRORE LA POSIZIONE DI CABINA RISULTA SBAGLIATA , CON CHIAMATA IN DISCESA VA TUTTO FUORI POSTO PUO DARE ERRORE, B5 .</t>
+  </si>
+  <si>
+    <t>"28" Contatto pieno  carico chiuso   ingresso FG</t>
+  </si>
+  <si>
+    <t>ok28</t>
+  </si>
+  <si>
+    <t>"29" Rele porte incollato ingresso CO</t>
+  </si>
+  <si>
+    <t>ok29</t>
+  </si>
+  <si>
+    <t>"30" Controllo porte CO aperto alla cad.di A1</t>
+  </si>
+  <si>
+    <t>ok30</t>
+  </si>
+  <si>
+    <t>"31" Controllo porte CO aperto alla cad.di C1</t>
+  </si>
+  <si>
+    <t>ok31</t>
+  </si>
+  <si>
+    <t>"32" Controllo porte CO aperto alla cad.di A2</t>
+  </si>
+  <si>
+    <t>ok32</t>
+  </si>
+  <si>
+    <t>"33" Controllo porte CO aperto alla cad.di C2</t>
+  </si>
+  <si>
+    <t>ok33</t>
+  </si>
+  <si>
+    <t>"34" Porte non aperte per contatto antipizzico</t>
+  </si>
+  <si>
+    <t>ok34UIUU</t>
+  </si>
+  <si>
+    <t>"35" Controllo porte CO chiuso con comando A1</t>
+  </si>
+  <si>
+    <t>ok35</t>
+  </si>
+  <si>
+    <t>"36" Controllo porte CO chiuso con comando C1</t>
+  </si>
+  <si>
+    <t>ok36</t>
+  </si>
+  <si>
+    <t>"37" Controllo porte CO chiuso con comando A2</t>
+  </si>
+  <si>
+    <t>ok37</t>
+  </si>
+  <si>
+    <t>"38" Controllo porte CO chiuso con comando C2</t>
+  </si>
+  <si>
+    <t>ok38</t>
+  </si>
+  <si>
+    <t>"39" Fine apertura FA non azionato dopo comando A1</t>
+  </si>
+  <si>
+    <t>ok39</t>
+  </si>
+  <si>
+    <t>"40" Fine chiusura FC non azionato dopo comando C1</t>
+  </si>
+  <si>
+    <t>ok40</t>
+  </si>
+  <si>
+    <t>"41" Fine apertura FA1non azionato dopo comando A2</t>
+  </si>
+  <si>
+    <t>ok41</t>
+  </si>
+  <si>
+    <t>"42" Fine chiusura FC1non azionato dopo comando C2</t>
+  </si>
+  <si>
+    <t>ok42</t>
+  </si>
+  <si>
+    <t>"43" Tensione manovra troppo bassa Ingresso CK</t>
+  </si>
+  <si>
+    <t>CONTROLLARE INTERVENTO TERMICA F0 MONTATA SUL QUADRO \ VERIFICARE EVENTUALI SICUREZZE POSTE PRIMA DEL MORSETTO CK  SU SCHEDA 1B</t>
+  </si>
+  <si>
+    <t>SU IMPIANTI DATATI CON INVERTER  ERRORE 43  INDICAVA ANCHE INVERTER IN GUASTO, NEL CASO PROVARE A RESETTARE INVERTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOLO SU 1B ( LA K NON MISURA LA TENSIONE ) MISURARE TENSIONE SU MORSETTO CK, SE LA TENSIONE MISURATA  E' SUPERIORE A 30V  NELLA PAGINA PRINCIPALE CERCA L' ARGOMENTO "ERRORE LETTURA TENSIONE  MANOVRA SU PROG2 ( MORSETTO CK  1B )" PER VERIFICARE ED EVENTUALMENTE TARARE LA LETTURA DELLA SCHEDA 1B. </t>
+  </si>
+  <si>
+    <t>"44" Ingr. sicurezze 2 senza tensione</t>
+  </si>
+  <si>
+    <t>Errore intervento extracorsa , crea fuori servizio memorizzato anche in mancanza tensione.</t>
+  </si>
+  <si>
+    <t>"45" Ingr. sicurezze 6 senza tensione</t>
+  </si>
+  <si>
+    <t>ok45</t>
+  </si>
+  <si>
+    <t>"46" Ingr. sicurezze 7 senza tensionealla partenza</t>
+  </si>
+  <si>
+    <t>ok46</t>
+  </si>
+  <si>
+    <t>"47" Ingr. sicurezze 9 senza tensionealla partenza</t>
+  </si>
+  <si>
+    <t>ok47</t>
+  </si>
+  <si>
+    <t>"48" Puls. manutenz. BD chiuso</t>
+  </si>
+  <si>
+    <t>ok48</t>
+  </si>
+  <si>
+    <t>"49" Puls. manutenz. BS chiuso</t>
+  </si>
+  <si>
+    <t>ok49</t>
+  </si>
+  <si>
+    <t>"50" Cont. magneti errato dopo arresto al piano</t>
+  </si>
+  <si>
+    <t>ok50</t>
+  </si>
+  <si>
+    <t>"51" Fine corsa porteFC e FA entrambi aperti</t>
+  </si>
+  <si>
+    <t>ok51</t>
+  </si>
+  <si>
+    <t>"52" Fine corsa porteFC1 e FA1 entrambi aperti</t>
+  </si>
+  <si>
+    <t>ok52</t>
+  </si>
+  <si>
+    <t>"53" Fine corsa porteFC3 e FA3 entrambi aperti</t>
+  </si>
+  <si>
+    <t>ok53</t>
+  </si>
+  <si>
+    <t>"54" Sensore ID non  aperto</t>
+  </si>
+  <si>
+    <t>ok54</t>
+  </si>
+  <si>
+    <t>"55" Sensore IS non  aperto</t>
+  </si>
+  <si>
+    <t>ok55</t>
+  </si>
+  <si>
+    <t>"56" Sensore ID non  chiuso</t>
+  </si>
+  <si>
+    <t>ok56</t>
+  </si>
+  <si>
+    <t>"57" Sensore IS non  chiuso</t>
+  </si>
+  <si>
+    <t>ok57</t>
+  </si>
+  <si>
+    <t>"58" Errore da consenso partenza/arresto inverter</t>
+  </si>
+  <si>
+    <t>ok58</t>
+  </si>
+  <si>
+    <t>"59" Linea sicurezze aperta in montaggio. Ingresso 7</t>
+  </si>
+  <si>
+    <t>ok59</t>
+  </si>
+  <si>
+    <t>"60" Tensione alim. scheda troppo bassa</t>
+  </si>
+  <si>
+    <t>ok60</t>
+  </si>
+  <si>
+    <t>"61" Limite corrente uscita scheda quadro</t>
+  </si>
+  <si>
+    <t>ok61</t>
+  </si>
+  <si>
+    <t>"62" Limite corrente uscita scheda cabina</t>
+  </si>
+  <si>
+    <t>ok62</t>
+  </si>
+  <si>
+    <t>"63" Con prenotazione allo stesso piano non parte in piccola velocità</t>
+  </si>
+  <si>
+    <t>CON SELETTORE IMPULSI, SE CABINA AL PIANO INFERIORE CON SOLO IS  , NON PARTE PIU NEANCHE CON UNA PRENOTAZIONE AD UN PIANO DIVERSO. PROVATO CON PROGRAMMAZIONE ID 32217 ( V5 V6 V7 )</t>
+  </si>
+  <si>
+    <t>"64" Cabina fuori piano alla fermata in salita</t>
+  </si>
+  <si>
+    <t>ok64</t>
+  </si>
+  <si>
+    <t>"65" Cabina fuori piano alla fermata in discesa</t>
+  </si>
+  <si>
+    <t>ok65</t>
+  </si>
+  <si>
+    <t>"66" Cabina uscita daIS e ID durante ritardo fermata</t>
+  </si>
+  <si>
+    <t>ok66</t>
+  </si>
+  <si>
+    <t>"67" Cabina uscita   dal piano nel   senso opposto</t>
+  </si>
+  <si>
+    <t>ok67</t>
+  </si>
+  <si>
+    <t>"68" Cabina fuori piano in rilivellamento salita</t>
+  </si>
+  <si>
+    <t>ok68</t>
+  </si>
+  <si>
+    <t>"69" Cabina fuori piano in rilivellamento discesa</t>
+  </si>
+  <si>
+    <t>ok69</t>
+  </si>
+  <si>
+    <t>"70" Ingr. sicurezze 9 senza tensionein rilivellam.</t>
+  </si>
+  <si>
+    <t>ok70</t>
+  </si>
+  <si>
+    <t>"71" Teleruttori non eccitati in rilivellamento</t>
+  </si>
+  <si>
+    <t>ok71</t>
+  </si>
+  <si>
+    <t>"72" Errore controllofotocellula allapartenza</t>
+  </si>
+  <si>
+    <t>ok72</t>
+  </si>
+  <si>
+    <t>"73" Errore posizionamento limiti manutenzione</t>
+  </si>
+  <si>
+    <t>ok73</t>
+  </si>
+  <si>
+    <t>"74" Intervento paracadute in discesa</t>
+  </si>
+  <si>
+    <t>ok74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"75" Intervento paracadute in salita   </t>
+  </si>
+  <si>
+    <t>ok75</t>
+  </si>
+  <si>
+    <t>"76" Chiamata sopra al piano estremosuperiore</t>
+  </si>
+  <si>
+    <t>ok76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"77" Chiamata sotto al piano estremoinferiore      </t>
+  </si>
+  <si>
+    <t>ok77</t>
+  </si>
+  <si>
+    <t>"78" Sensore ID chiuso all entrata nel rif. RD</t>
+  </si>
+  <si>
+    <t>ok78</t>
+  </si>
+  <si>
+    <t>"79" Sensore IS chiuso all entrata nel rif. RS</t>
+  </si>
+  <si>
+    <t>ok79</t>
+  </si>
+  <si>
+    <t>"80" Manca ID al piano in salita</t>
+  </si>
+  <si>
+    <t>ok80</t>
+  </si>
+  <si>
+    <t>"81" Manca ID al piano in discesa</t>
+  </si>
+  <si>
+    <t>ok81</t>
+  </si>
+  <si>
+    <t>"82" Manca IS al piano in salita</t>
+  </si>
+  <si>
+    <t>ok82</t>
+  </si>
+  <si>
+    <t>"83" Manca IS al piano in discesa</t>
+  </si>
+  <si>
+    <t>ok83</t>
+  </si>
+  <si>
+    <t>"84" Manca ID cambio velocita</t>
+  </si>
+  <si>
+    <t>ok84</t>
+  </si>
+  <si>
+    <t>"85" Manca IS cambio velocita</t>
+  </si>
+  <si>
+    <t>ok85</t>
+  </si>
+  <si>
+    <t>"86" Mancano imp. A/BCon emerg. est. blocco sch.emerg</t>
+  </si>
+  <si>
+    <t>ok86FFF</t>
+  </si>
+  <si>
+    <t>"87" Mancata tensione al morsetto 7 c/cabina in marcia</t>
+  </si>
+  <si>
+    <t>ok87</t>
+  </si>
+  <si>
+    <t>"88" Stop da emerg. esterna per vel.non adeguata</t>
+  </si>
+  <si>
+    <t>ok88</t>
+  </si>
+  <si>
+    <t>"89" Mancata tensione al morsetto 9 c/cabina in marcia</t>
+  </si>
+  <si>
+    <t>ok89</t>
+  </si>
+  <si>
+    <t>"90" Attivato blocco in fuori serv. ingresso ENC</t>
+  </si>
+  <si>
+    <t>ok90</t>
+  </si>
+  <si>
+    <t>"91" Scaduto tempo conteggio IS/ID in piccola veloc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CON VANO IMPULSI SE PARTE IN ALTA E PASSA IN V2 CONTA T. BASSA VELOCITA' SE INVECE PARTE IN V2 CONTA IL T. DI ALTA TEST ESEGUITI CON B335.F  </t>
+  </si>
+  <si>
+    <t>FUNE GRL CON VANO IMPULSI SE PARTE IN ALTA E PASSA IN V2 CONTA T. BASSA VELOCITA' SE INVECE PARTE IN V2 CONTA IL T. DI ALTA TEST ESEGUITI CON B335.F  :   \\\       ALLA PRIMA ACCENSIONE PARTENDO SOPRA RIF. :       SE NON ARRIVO AL PIANO DOPO T. BASSA ( 15 SEC ) VA IN 91  SENZA FUORI SERVIZIO. SOTTO RIF PARTE IN V2 CONTINUA PER 40 SEC ( ANCHE SE T. BASSA IMPOSTATO A 15 SEC  ) SE NON ARRIVA AL PIANO VA IN FUORI SERVIZIO CON F91.      \\\\\\      ALLA PRIMA ACCENSIONE PARTENDO SOTTO RIF :          DOPO 40 SEC ( ANCHE SE T. BASSA IMPOSTATO A 15 SEC)  DA ERRORE  91 SENZA FUORI SERVIZIO  . CON ULTERIORE CHIAMATA  PARTE IN BASSA DOPO 40 SEC ( ANCHE SE T. BASSA IMPOSTATO A 15 SEC )  DA ERRORE 91 CON FUORI SERVIZIO  \\\\\\\\         PARTO DA PIANO 0 CON CHIAMATA  PIANO 1 :          PARTO IN V7 , AL CAMBIO VELOCITA PASSA IN V2 , NON ARRIVO AL PIANO DOPO T. BASSA ( 15 SEC ) SI SFASA, DA ERRORE 91 POSIZIONE 32 SENZA FUORI SERVIZIO . CON ULTERIORE  CHIAMATA VA IN ALTA , PASSA IN V2 SU RIFASATORE  , SE NON ARRIVO AL PIANO DOPO T. BASSA ( 15 SEC ) VA IN 91 ANCORA SENZA FUORI SERVIZIO. SOTTO RIF. PARTE IN V2 CONTINUA PER 40 SEC  ( ANCHE SE T. BASSA IMPOSTATO A 15 SEC ) SE NON ARRIVA AL PIANO VA IN FUORI SERVIZIO CON F91.</t>
+  </si>
+  <si>
+    <t>SU IDRAULICI :   \\\    PARTO DA PIANO 0 CON CHIAMATA  PIANO 1 :          PARTO IN V7 , AL CAMBIO VELOCITA PASSA IN V2 , NON ARRIVO AL PIANO DOPO T. BASSA ( 15 SEC ) SI SFASA, DA ERRORE 91 POSIZIONE 32 E FUORI SERVIZIO, SI SFASA PARTE IN ALTA PER RIMANDO AL PIANO INFERIORE , PASSA IN V2  SU RIFASATORE ARRIVA AL PIANO RIMANE IN FUORI SERVIZIO CON F91. \\\\\\    PARTO DA PIANO 3 VERSO 0 :  SE SI APRE RIFASATORE PER UN ATTIMO LA SCHEDA PASSA IN BASSA E IL DS1 INDICA PIANO 0, PROSEGUE FINO AL PRIMO IS  + ID CHE TROVA E SI FERMA  ( ANCHE CON RIF CHIUSO ) RIPARTE PER RIFASAMENTO IN ALTA VELOCITA' .</t>
+  </si>
+  <si>
+    <t>"92" Scaduto tempo rilivellamento</t>
+  </si>
+  <si>
+    <t>ok92</t>
+  </si>
+  <si>
+    <t>"93" Non chiude per fotocellula ingresso FT/FT1</t>
+  </si>
+  <si>
+    <t>ok93</t>
+  </si>
+  <si>
+    <t>"94" Non chiude per costola mobile  ingresso CM/CM1</t>
+  </si>
+  <si>
+    <t>ok94</t>
+  </si>
+  <si>
+    <t>"95" Non chiude per puls. apertura  ingresso PAP</t>
+  </si>
+  <si>
+    <t>ok95</t>
+  </si>
+  <si>
+    <t>"96" Temperatura locale macchina inferiore a val.min.</t>
+  </si>
+  <si>
+    <t>ok96</t>
+  </si>
+  <si>
+    <t>"97" Temperatura locale macchina superiore a val.max.</t>
+  </si>
+  <si>
+    <t>ok97</t>
+  </si>
+  <si>
+    <t>"98" Velocita eccessiva in emerg./B  Vedi menu O/38</t>
+  </si>
+  <si>
+    <t>ok98</t>
+  </si>
+  <si>
+    <t>"99"  Programmazione errata</t>
+  </si>
+  <si>
+    <t>ok99</t>
+  </si>
+  <si>
+    <t>"A0" Prova valvole non eseguita dopo tempo previsto</t>
+  </si>
+  <si>
+    <t>ok100</t>
+  </si>
+  <si>
+    <t>"A1" Ingresso CT non aperto durante  prova valvole</t>
+  </si>
+  <si>
+    <t>ok101</t>
+  </si>
+  <si>
+    <t>"A2" Guasto tenuta VD2 durante prova valvole</t>
+  </si>
+  <si>
+    <t>ok102</t>
+  </si>
+  <si>
+    <t>"A3" Guasto tenuta VD1 durante prova valvole</t>
+  </si>
+  <si>
+    <t>ok103</t>
+  </si>
+  <si>
+    <t>"A4" Ingresso controllo emendamento A3 aperto</t>
+  </si>
+  <si>
+    <t>ok104</t>
+  </si>
+  <si>
+    <t>"A5" Sensori IS/ID azionati fuori piano senza comandi</t>
+  </si>
+  <si>
+    <t>ok105</t>
+  </si>
+  <si>
+    <t>26 5 2025  il problema si è presentato a causa di fili non stretti sul magnetotermico generale,in caso di errore A5 verificare bene tutto il circuito di alimentazione</t>
+  </si>
+  <si>
+    <t>"A6" Cabina uscita dal piano con porte aperte</t>
+  </si>
+  <si>
+    <t>ok106</t>
+  </si>
+  <si>
+    <t>"A7" Segnali RDY/RUN da valvola NGV entrambi on</t>
+  </si>
+  <si>
+    <t>ok107</t>
+  </si>
+  <si>
+    <t>"A8" Segnali RDY/RUN da valvola NGV entrambi off</t>
+  </si>
+  <si>
+    <t>ok108</t>
+  </si>
+  <si>
+    <t>"A9" Consenso attivazione valvola discesa Hydronic</t>
+  </si>
+  <si>
+    <t>ok109</t>
+  </si>
+  <si>
+    <t>"B0" ERR B0</t>
+  </si>
+  <si>
+    <t>ok110</t>
+  </si>
+  <si>
+    <t>"B1" Microsw. controllo freno M1 in posizione errata</t>
+  </si>
+  <si>
+    <t>ok111</t>
+  </si>
+  <si>
+    <t>"B2" Microsw. controllo freno M2 in posizione errata</t>
+  </si>
+  <si>
+    <t>ok112</t>
+  </si>
+  <si>
+    <t>"B3" Microsw. controllo freno M1 e M2in posiz. Errata</t>
+  </si>
+  <si>
+    <t>ok113</t>
+  </si>
+  <si>
+    <t>"B4" ERR B4</t>
+  </si>
+  <si>
+    <t>ok114</t>
+  </si>
+  <si>
+    <t>"B5" ERR B5</t>
+  </si>
+  <si>
+    <t>PPPPPPYYHYHYHYH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SU GRL IN CASO DI ERRORE ALLA FERMATA IL CONTEGGIO DEI PIANI VIENE SBALLATO, ( ES. IMP. 2F ,SI FERMA SU IS+IS CON ERR 27 , SE SI RESETTA ERRORE SI VEDE CHE LA SCHEDA INDICA 002, IN REALTA IMPOSSIBILE PERCHE' SE 2 FERMATE AL MASSIMO DEVE INDICARE 01 O -- SE SFASATO.DA LI IN POI POSSONO SEGUIRE UN DIVERSI ERRORI OLTRE A B5 , CONTEGGIO ( 50 ) O ALTRO )   , VERIFICARE EVENTUALI PROBLEMI IN FERMATA </t>
+  </si>
+  <si>
+    <t>"B6" Rifasatore velocita' intermedia V6 chiuso : Rifasatore non aperto (RFI28) rallentamento piano estremo</t>
+  </si>
+  <si>
+    <t>"B7" Rifasatore alta velocita' V7  chiuso : Rifasatore non aperto ( SR o DR ) rallentamento piano estremo , in codice velocita' 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rifasatore non aperto al piano estremo nel momento del cambio velocita' : durnate una corsa normale la scheda al piano estremo cambierebbe velocita'  alla distanza impostata come a tutti gli altri piani ma in realta'  in quel punto invece di cambiare verifica che sia gia' in bassa grazie all intervento del ifasatore interessato che deve risultare aperto, se alla distanza del cambio il rifasatore risulta chiuso, quindi la scheda si trova ancora in alta velocità, viene segnalato errore ed eseguito il cambio grazie al conteggio impulsi. </t>
+  </si>
+  <si>
+    <t>Nel caso non fosse stato eseguito apprendimento del vano eseguire la procedura per momorizzare l' effetiva posizione dei magneti del vano seguendo le istruzioni del manuale</t>
+  </si>
+  <si>
+    <t>In caso di errore dopo aver effettuato l' apprendimento del vano  verificare : distanza rallentamento in V7 impostata nel menù 8.4.07 , verificare che la posizone del rifasatore sia 150mm più lontana dal piano es se in 8.4.07 = 1650 il rifasatore deve essere a 1800mm dal piano,nel caso la scheda arrivi a 1650mm dal piano estremo e il rifasatore non fosse aperto errore B7</t>
+  </si>
+  <si>
+    <t>"B8" Blocco numero corse : Blocco impianto per raggiungimento del limite numero corse programmato</t>
+  </si>
+  <si>
+    <t>"B9" Blocco per accessi errati : blocco impianto per il raggiungimento del numero limite di 5 inserimenti passoword errati</t>
+  </si>
+  <si>
+    <t>"C0" Blocco per guasto inverter : blocco impianto per guasto inverter o altro dispositivo</t>
+  </si>
+  <si>
+    <t>"C1" Sic.8 porte cabina chiusa durante prova EN81-20</t>
+  </si>
+  <si>
+    <t>SEQUENZA IN CUI DA ERRORE "C1" =Con  comando apertura , si spengono le sicurezze 7\9 ,in fine apertura si eccita KTP , se si accendono sicurezze 7\9 , prima di richiudere la scheda da errore . Questo comportamento avviene se è presente un cavallotto su blocchi, all apertura le porte cabina interrompono le sicurezze e la scheda non è in grado di verificare le sicurezze dei blocchi. In fine apertura la scheda comanda KTP che crea un ponte tra si 6 e sicurezza 9, se in questa condizione si attiva sicurezza 7 significa che tra 8\9 è presente un ponte o il  blocco non si è aperto. Fuori servizio al primo errore rilevato.</t>
+  </si>
+  <si>
+    <t>IN CASO DI SERRATURA ATTENZIONE A FINE EMERGENZA : COMANDO SERRATURA VIENE STACCATO DOPO UN PO  DI TEMPO QUINDI SE TORNA LA RETE E LA SCHEDA NON SI SPEGNE SI TROVA SIC7 PRIMA DI CHIUDERE E VA IN FC1 VEDI ID 33301 SW B335.F</t>
+  </si>
+  <si>
+    <t>"C2" Controllo porte ( FI84 ) chiuso in fine apertura EN81-20</t>
+  </si>
+  <si>
+    <t>Con porta aperta  ,in fine apertura , l' ingresso con funzione FI84 risulta attivo ( led "X6" SU SCHEDA 1C  acceso ) prima dichiudere la scheda segnala errore FC2. Questo indica che il contatto supplementare di porta chiusa posto sull operatore non si è aperto con porta in fine apertura . Fuori servizio al primo errore rilevato.</t>
+  </si>
+  <si>
+    <t>"C3" Controllo porte ( FI84 ) aperto in fine chiusura EN81-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con chiamata  , questo errore non viene segnalato per chiusura in stazionamento , la scheda chiude le porte se dopo chiusura l' ingresso programmato con funzione FI84 ( in genere ingresso X6 su scheda 1C ) non si attiva e il led rimane spento la scheda non comanda la marcia, dopo una decina di secondi segnala errore "C3" ma non va fuori servizio. </t>
+  </si>
+  <si>
+    <t>"C4" Sic.8 porte cabina chiusa dopo apertura EN81-20</t>
+  </si>
+  <si>
+    <t>SEQUENZA IN CUI DA ERRORE "C4" =Con  comando apertura , si spengne solo la curezza 9 mentre la sicurezza 7 rimane accesa, in fine apertura la scheda da errore "C4" . Questo comportamento avviene se è presente un cavallotto su porte cabina, all apertura le porte cabina non interrompono la sicurezza 7,  la scheda attende il fine apertura per essere sicura che le porte siano aperte , in quel momento se la sicurezza 7 è ancora attiva la scheda segnala errore "C4". Fuori servizio al primo errore rilevato.</t>
+  </si>
+  <si>
+    <t>"C5" Sic.9 non alimentata durante prova EN81-20</t>
+  </si>
+  <si>
+    <t>ok120</t>
+  </si>
+  <si>
+    <t>"C6"</t>
+  </si>
+  <si>
+    <t>ok121</t>
+  </si>
+  <si>
+    <t>"C7"</t>
+  </si>
+  <si>
+    <t>ok122</t>
+  </si>
+  <si>
+    <t>"C8"</t>
+  </si>
+  <si>
+    <t>ok123</t>
+  </si>
+  <si>
+    <t>"C9"</t>
+  </si>
+  <si>
+    <t>hhhh</t>
+  </si>
+  <si>
+    <t>hh</t>
+  </si>
+  <si>
+    <t>"D0"</t>
+  </si>
+  <si>
+    <t>"D1"</t>
+  </si>
+  <si>
+    <t>STATO IMPIANTO CON DS1  = 2</t>
+  </si>
+  <si>
+    <t>CHIUSURA PORTE IMPEDITA PER INTERVENTO FOTOCELLULA \ COSTOLA MOBILE \ PULSANTE APERTURA \ ACCOSTAMENTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATTENZIONE IN CASO DI IMPIANTO FUNE CON 3VF :ANCHE CON  INVERTER IN ALLARME E CABINA AL PIANO LA SCHEDA INDICA DS1 = 2 </t>
+  </si>
+  <si>
+    <t>DESCRIZIONE</t>
+  </si>
+  <si>
+    <t>AIUTO1</t>
+  </si>
+  <si>
+    <t>AIUTO2</t>
+  </si>
+  <si>
+    <t>AIUTO3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -86,16 +905,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -103,12 +934,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -124,10 +977,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -446,53 +1295,1160 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D0AEF67-D3C2-46B7-9D09-D4D935291FC8}">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79EA708F-AAD2-4A43-89B4-E20769B6A444}">
+  <dimension ref="A1:E133"/>
+  <sheetFormatPr defaultColWidth="25.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.140625" customWidth="1"/>
+    <col min="1" max="1" width="139.85546875" customWidth="1"/>
+    <col min="4" max="4" width="72.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="D2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3">
+        <v>6555555555</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B4" t="s">
         <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+      <c r="E9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B34" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B36" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B38" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B44" t="s">
+        <v>97</v>
+      </c>
+      <c r="C44" t="s">
+        <v>98</v>
+      </c>
+      <c r="D44" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B45" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B46" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B47" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B48" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B49" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B50" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B51" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B52" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B53" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B54" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B55" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B56" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B57" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B58" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B59" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B60" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B61" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B62" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B63" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E64" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B65" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B66" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B67" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B68" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B69" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B70" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B71" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B72" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B73" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B74" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B75" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B76" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B77" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B78" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B79" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B80" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B81" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B82" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B83" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B84" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B85" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B86" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B87" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B88" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B89" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B90" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B91" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B92" t="s">
+        <v>195</v>
+      </c>
+      <c r="C92" t="s">
+        <v>196</v>
+      </c>
+      <c r="D92" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B93" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B94" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B95" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B96" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B97" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B98" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B99" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B100" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B101" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B102" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B103" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B104" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B105" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B106" t="s">
+        <v>225</v>
+      </c>
+      <c r="C106" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B107" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B108" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B109" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B110" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B111" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B112" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B113" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B114" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B115" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B116" t="s">
+        <v>246</v>
+      </c>
+      <c r="C116" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B118" t="s">
+        <v>250</v>
+      </c>
+      <c r="C118" t="s">
+        <v>251</v>
+      </c>
+      <c r="D118" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B122" t="s">
+        <v>257</v>
+      </c>
+      <c r="C122" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B123" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B124" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B125" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B126" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B127" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B128" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B129" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B130" t="s">
+        <v>274</v>
+      </c>
+      <c r="C130" t="s">
+        <v>274</v>
+      </c>
+      <c r="D130" t="s">
+        <v>275</v>
+      </c>
+      <c r="E130" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B133" t="s">
+        <v>279</v>
+      </c>
+      <c r="C133" t="s">
+        <v>280</v>
       </c>
     </row>
   </sheetData>
